--- a/LISTAS/ma/SOPAPA COMUN Y GIGANTE DISMAY.xlsx
+++ b/LISTAS/ma/SOPAPA COMUN Y GIGANTE DISMAY.xlsx
@@ -846,14 +846,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="36" t="n">
-        <v>45182.62504407279</v>
+        <v>45216</v>
       </c>
       <c r="E1" s="3" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="29">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -905,16 +901,6 @@
       <c r="C12" s="27" t="n"/>
       <c r="D12" s="27" t="n"/>
     </row>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
     <row r="23">
       <c r="C23" s="13" t="n"/>
     </row>
@@ -996,8 +982,6 @@
     <row r="32">
       <c r="A32" s="16" t="n"/>
     </row>
-    <row r="33"/>
-    <row r="34"/>
     <row r="35" ht="18" customHeight="1" s="29">
       <c r="A35" s="31" t="n"/>
       <c r="B35" s="31" t="n"/>
@@ -1017,34 +1001,30 @@
     <row r="39" ht="19.5" customHeight="1" s="29">
       <c r="B39" s="28" t="n"/>
     </row>
-    <row r="40"/>
-    <row r="41"/>
     <row r="42" ht="19.5" customHeight="1" s="29">
       <c r="A42" s="6" t="n"/>
     </row>
-    <row r="43"/>
     <row r="44">
       <c r="A44" s="4" t="n"/>
     </row>
-    <row r="45"/>
     <row r="46">
       <c r="A46" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="B39:C39"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B38:C38"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A10:D10"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/SOPAPA COMUN Y GIGANTE DISMAY.xlsx
+++ b/LISTAS/ma/SOPAPA COMUN Y GIGANTE DISMAY.xlsx
@@ -846,7 +846,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="36" t="n">
-        <v>45216</v>
+        <v>45217</v>
       </c>
       <c r="E1" s="3" t="n"/>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="C29" s="25" t="n"/>
       <c r="D29" s="21" t="n">
-        <v>298.5</v>
+        <v>271.635</v>
       </c>
     </row>
     <row r="30" ht="19.5" customHeight="1" s="29">
@@ -972,7 +972,7 @@
       </c>
       <c r="C30" s="25" t="n"/>
       <c r="D30" s="21" t="n">
-        <v>223.526</v>
+        <v>203.40866</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1" s="29">

--- a/LISTAS/ma/SOPAPA COMUN Y GIGANTE DISMAY.xlsx
+++ b/LISTAS/ma/SOPAPA COMUN Y GIGANTE DISMAY.xlsx
@@ -846,7 +846,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="36" t="n">
-        <v>45217</v>
+        <v>45231</v>
       </c>
       <c r="E1" s="3" t="n"/>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="C29" s="25" t="n"/>
       <c r="D29" s="21" t="n">
-        <v>271.635</v>
+        <v>298.5</v>
       </c>
     </row>
     <row r="30" ht="19.5" customHeight="1" s="29">
@@ -972,7 +972,7 @@
       </c>
       <c r="C30" s="25" t="n"/>
       <c r="D30" s="21" t="n">
-        <v>203.40866</v>
+        <v>223.526</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1" s="29">

--- a/LISTAS/ma/SOPAPA COMUN Y GIGANTE DISMAY.xlsx
+++ b/LISTAS/ma/SOPAPA COMUN Y GIGANTE DISMAY.xlsx
@@ -846,7 +846,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="36" t="n">
-        <v>45231</v>
+        <v>45232</v>
       </c>
       <c r="E1" s="3" t="n"/>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="C29" s="25" t="n"/>
       <c r="D29" s="21" t="n">
-        <v>298.5</v>
+        <v>300</v>
       </c>
     </row>
     <row r="30" ht="19.5" customHeight="1" s="29">

--- a/LISTAS/ma/SOPAPA COMUN Y GIGANTE DISMAY.xlsx
+++ b/LISTAS/ma/SOPAPA COMUN Y GIGANTE DISMAY.xlsx
@@ -846,7 +846,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="36" t="n">
-        <v>45232</v>
+        <v>45234</v>
       </c>
       <c r="E1" s="3" t="n"/>
     </row>

--- a/LISTAS/ma/SOPAPA COMUN Y GIGANTE DISMAY.xlsx
+++ b/LISTAS/ma/SOPAPA COMUN Y GIGANTE DISMAY.xlsx
@@ -846,7 +846,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="36" t="n">
-        <v>45234</v>
+        <v>45237</v>
       </c>
       <c r="E1" s="3" t="n"/>
     </row>

--- a/LISTAS/ma/SOPAPA COMUN Y GIGANTE DISMAY.xlsx
+++ b/LISTAS/ma/SOPAPA COMUN Y GIGANTE DISMAY.xlsx
@@ -846,7 +846,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="36" t="n">
-        <v>45237</v>
+        <v>45238</v>
       </c>
       <c r="E1" s="3" t="n"/>
     </row>
@@ -1012,19 +1012,19 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A10:D10"/>
     <mergeCell ref="B38:C38"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="B37:C37"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B28:C28"/>
+    <mergeCell ref="A9:D9"/>
     <mergeCell ref="B36:C36"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B29:C29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/SOPAPA COMUN Y GIGANTE DISMAY.xlsx
+++ b/LISTAS/ma/SOPAPA COMUN Y GIGANTE DISMAY.xlsx
@@ -846,7 +846,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="36" t="n">
-        <v>45238</v>
+        <v>45252</v>
       </c>
       <c r="E1" s="3" t="n"/>
     </row>
@@ -1012,19 +1012,19 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="A1:D1"/>
     <mergeCell ref="B38:C38"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B29:C29"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="B37:C37"/>
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A10:D10"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B29:C29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/SOPAPA COMUN Y GIGANTE DISMAY.xlsx
+++ b/LISTAS/ma/SOPAPA COMUN Y GIGANTE DISMAY.xlsx
@@ -846,7 +846,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="36" t="n">
-        <v>45252</v>
+        <v>45253</v>
       </c>
       <c r="E1" s="3" t="n"/>
     </row>

--- a/LISTAS/ma/SOPAPA COMUN Y GIGANTE DISMAY.xlsx
+++ b/LISTAS/ma/SOPAPA COMUN Y GIGANTE DISMAY.xlsx
@@ -1012,19 +1012,19 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A10:D10"/>
     <mergeCell ref="B38:C38"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="B37:C37"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B28:C28"/>
+    <mergeCell ref="A9:D9"/>
     <mergeCell ref="B36:C36"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B29:C29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/SOPAPA COMUN Y GIGANTE DISMAY.xlsx
+++ b/LISTAS/ma/SOPAPA COMUN Y GIGANTE DISMAY.xlsx
@@ -846,7 +846,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="36" t="n">
-        <v>45253</v>
+        <v>45254</v>
       </c>
       <c r="E1" s="3" t="n"/>
     </row>
@@ -1012,19 +1012,19 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="A1:D1"/>
     <mergeCell ref="B38:C38"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B29:C29"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="B37:C37"/>
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A10:D10"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B29:C29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/SOPAPA COMUN Y GIGANTE DISMAY.xlsx
+++ b/LISTAS/ma/SOPAPA COMUN Y GIGANTE DISMAY.xlsx
@@ -846,7 +846,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="36" t="n">
-        <v>45254</v>
+        <v>45256</v>
       </c>
       <c r="E1" s="3" t="n"/>
     </row>

--- a/LISTAS/ma/SOPAPA COMUN Y GIGANTE DISMAY.xlsx
+++ b/LISTAS/ma/SOPAPA COMUN Y GIGANTE DISMAY.xlsx
@@ -846,7 +846,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="36" t="n">
-        <v>45256</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="3" t="n"/>
     </row>

--- a/LISTAS/ma/SOPAPA COMUN Y GIGANTE DISMAY.xlsx
+++ b/LISTAS/ma/SOPAPA COMUN Y GIGANTE DISMAY.xlsx
@@ -846,10 +846,14 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="36" t="n">
-        <v>45266</v>
+        <v>45226.6515736497</v>
       </c>
       <c r="E1" s="3" t="n"/>
     </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="29">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -901,6 +905,16 @@
       <c r="C12" s="27" t="n"/>
       <c r="D12" s="27" t="n"/>
     </row>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
     <row r="23">
       <c r="C23" s="13" t="n"/>
     </row>
@@ -956,7 +970,7 @@
       </c>
       <c r="C29" s="25" t="n"/>
       <c r="D29" s="21" t="n">
-        <v>300</v>
+        <v>298.5</v>
       </c>
     </row>
     <row r="30" ht="19.5" customHeight="1" s="29">
@@ -972,7 +986,7 @@
       </c>
       <c r="C30" s="25" t="n"/>
       <c r="D30" s="21" t="n">
-        <v>223.526</v>
+        <v>263.76</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1" s="29">
@@ -982,6 +996,8 @@
     <row r="32">
       <c r="A32" s="16" t="n"/>
     </row>
+    <row r="33"/>
+    <row r="34"/>
     <row r="35" ht="18" customHeight="1" s="29">
       <c r="A35" s="31" t="n"/>
       <c r="B35" s="31" t="n"/>
@@ -1001,30 +1017,34 @@
     <row r="39" ht="19.5" customHeight="1" s="29">
       <c r="B39" s="28" t="n"/>
     </row>
+    <row r="40"/>
+    <row r="41"/>
     <row r="42" ht="19.5" customHeight="1" s="29">
       <c r="A42" s="6" t="n"/>
     </row>
+    <row r="43"/>
     <row r="44">
       <c r="A44" s="4" t="n"/>
     </row>
+    <row r="45"/>
     <row r="46">
       <c r="A46" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="A12:D12"/>
     <mergeCell ref="B39:C39"/>
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B37:C37"/>
     <mergeCell ref="B38:C38"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B35:C35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
